--- a/patchr/resources/PLATES_v2.0.0/AB[BATCH_ID].3SARS.xlsx
+++ b/patchr/resources/PLATES_v2.0.0/AB[BATCH_ID].3SARS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10212"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10312"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tpd0001/github/watch-wv/analysis/resources/PLATES_v2.0.0/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tpd0001/github/watch-wv/patchr/resources/PLATES_v2.0.0/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E3576DF-193E-6148-B803-95BA44026EDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F582EA61-EE19-5B4A-B961-03F269321D51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="201">
   <si>
     <t>Assay</t>
   </si>
@@ -394,19 +394,10 @@
     <t>Method Lot ID</t>
   </si>
   <si>
-    <t>Target Category</t>
-  </si>
-  <si>
     <t>Target Genetic Locus</t>
   </si>
   <si>
     <t>TD</t>
-  </si>
-  <si>
-    <t>Control 1 Calculated Copies Per uL Reaction</t>
-  </si>
-  <si>
-    <t>Control 2 Calculated Copies Per uL Reaction</t>
   </si>
   <si>
     <t>Input uL</t>
@@ -419,9 +410,6 @@
   </si>
   <si>
     <t>Control 2 Well</t>
-  </si>
-  <si>
-    <t>Target Calculated Copies Per uL Reaction</t>
   </si>
   <si>
     <t>Batch Type</t>
@@ -452,9 +440,6 @@
   </si>
   <si>
     <t>2.0</t>
-  </si>
-  <si>
-    <t>QX Manager Version</t>
   </si>
   <si>
     <t>Zoo QX200</t>
@@ -643,13 +628,22 @@
     <t>Multiple</t>
   </si>
   <si>
-    <t>Target Host</t>
-  </si>
-  <si>
     <t>Mpox Virus I (MPXV)</t>
   </si>
   <si>
     <t>Mpox Virus II (MPXV)</t>
+  </si>
+  <si>
+    <t>Control 2 Predicted Copies Per uL Reaction</t>
+  </si>
+  <si>
+    <t>Control 1 Predicted Copies Per uL Reaction</t>
+  </si>
+  <si>
+    <t>Target Predicted Copies Per uL Reaction</t>
+  </si>
+  <si>
+    <t>Analysis Software Version</t>
   </si>
 </sst>
 </file>
@@ -1632,7 +1626,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D39BBE7-67FA-5442-B147-F43387474561}">
-  <dimension ref="A1:Z927"/>
+  <dimension ref="A1:Z921"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="51.5703125" style="43" customWidth="1"/>
@@ -1644,7 +1638,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="39" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B1" s="40" t="s">
         <v>0</v>
@@ -1676,7 +1670,7 @@
     </row>
     <row r="2" spans="1:26" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="44" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B2" s="45" t="s">
         <v>80</v>
@@ -1743,7 +1737,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="42" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C4" s="48"/>
       <c r="D4" s="42"/>
@@ -1775,7 +1769,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="46" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C5" s="42"/>
       <c r="D5" s="42"/>
@@ -1804,10 +1798,10 @@
     </row>
     <row r="6" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="42" t="s">
-        <v>137</v>
+        <v>200</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C6" s="42"/>
       <c r="D6" s="42"/>
@@ -1836,10 +1830,10 @@
     </row>
     <row r="7" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="71" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B7" s="71" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C7" s="42"/>
       <c r="D7" s="42"/>
@@ -1868,13 +1862,13 @@
     </row>
     <row r="8" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="42" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B8" s="42">
         <v>5</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D8" s="42"/>
       <c r="E8" s="42"/>
@@ -1902,7 +1896,7 @@
     </row>
     <row r="9" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="46" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B9" s="46">
         <v>20</v>
@@ -1969,7 +1963,7 @@
         <v>84</v>
       </c>
       <c r="B11" s="46" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C11" s="49"/>
       <c r="D11" s="42"/>
@@ -2030,7 +2024,7 @@
     </row>
     <row r="13" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="46" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B13" s="46" t="s">
         <v>102</v>
@@ -2065,7 +2059,7 @@
         <v>115</v>
       </c>
       <c r="B14" s="42" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="C14" s="49"/>
       <c r="D14" s="42"/>
@@ -2097,7 +2091,7 @@
         <v>116</v>
       </c>
       <c r="B15" s="72" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C15" s="67"/>
       <c r="D15" s="42"/>
@@ -2126,7 +2120,7 @@
     </row>
     <row r="16" spans="1:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="69" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B16" s="70" t="s">
         <v>56</v>
@@ -2158,7 +2152,7 @@
     </row>
     <row r="17" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="68" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B17" s="68" t="s">
         <v>58</v>
@@ -2220,52 +2214,52 @@
       <c r="Z18" s="42"/>
     </row>
     <row r="19" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="52" t="s">
-        <v>200</v>
+      <c r="A19" s="53" t="s">
+        <v>117</v>
       </c>
-      <c r="B19" s="52" t="s">
-        <v>196</v>
+      <c r="B19" s="54" t="s">
+        <v>188</v>
       </c>
       <c r="C19"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="42"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="42"/>
-      <c r="I19" s="42"/>
-      <c r="J19" s="42"/>
-      <c r="K19" s="42"/>
-      <c r="L19" s="42"/>
-      <c r="M19" s="42"/>
-      <c r="N19" s="42"/>
-      <c r="O19" s="42"/>
-      <c r="P19" s="42"/>
-      <c r="Q19" s="42"/>
-      <c r="R19" s="42"/>
-      <c r="S19" s="42"/>
-      <c r="T19" s="42"/>
-      <c r="U19" s="42"/>
-      <c r="V19" s="42"/>
-      <c r="W19" s="42"/>
-      <c r="X19" s="42"/>
-      <c r="Y19" s="42"/>
-      <c r="Z19" s="42"/>
     </row>
     <row r="20" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="53" t="s">
-        <v>118</v>
+      <c r="A20" s="52" t="s">
+        <v>78</v>
       </c>
-      <c r="B20" s="54" t="s">
-        <v>193</v>
+      <c r="B20" s="52" t="s">
+        <v>73</v>
       </c>
       <c r="C20"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="42"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="42"/>
+      <c r="H20" s="42"/>
+      <c r="I20" s="42"/>
+      <c r="J20" s="42"/>
+      <c r="K20" s="42"/>
+      <c r="L20" s="42"/>
+      <c r="M20" s="42"/>
+      <c r="N20" s="42"/>
+      <c r="O20" s="42"/>
+      <c r="P20" s="42"/>
+      <c r="Q20" s="42"/>
+      <c r="R20" s="42"/>
+      <c r="S20" s="42"/>
+      <c r="T20" s="42"/>
+      <c r="U20" s="42"/>
+      <c r="V20" s="42"/>
+      <c r="W20" s="42"/>
+      <c r="X20" s="42"/>
+      <c r="Y20" s="42"/>
+      <c r="Z20" s="42"/>
     </row>
     <row r="21" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="52" t="s">
-        <v>117</v>
+        <v>199</v>
       </c>
-      <c r="B21" s="52" t="s">
-        <v>98</v>
+      <c r="B21" s="52">
+        <v>0</v>
       </c>
       <c r="C21"/>
       <c r="D21" s="42"/>
@@ -2293,46 +2287,22 @@
       <c r="Z21" s="42"/>
     </row>
     <row r="22" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="52" t="s">
-        <v>78</v>
+      <c r="A22" s="55" t="s">
+        <v>81</v>
       </c>
-      <c r="B22" s="52" t="s">
-        <v>73</v>
+      <c r="B22" s="56" t="s">
+        <v>91</v>
       </c>
-      <c r="C22"/>
-      <c r="D22" s="42"/>
-      <c r="E22" s="42"/>
-      <c r="F22" s="42"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="42"/>
-      <c r="I22" s="42"/>
-      <c r="J22" s="42"/>
-      <c r="K22" s="42"/>
-      <c r="L22" s="42"/>
-      <c r="M22" s="42"/>
-      <c r="N22" s="42"/>
-      <c r="O22" s="42"/>
-      <c r="P22" s="42"/>
-      <c r="Q22" s="42"/>
-      <c r="R22" s="42"/>
-      <c r="S22" s="42"/>
-      <c r="T22" s="42"/>
-      <c r="U22" s="42"/>
-      <c r="V22" s="42"/>
-      <c r="W22" s="42"/>
-      <c r="X22" s="42"/>
-      <c r="Y22" s="42"/>
-      <c r="Z22" s="42"/>
+      <c r="C22" s="51"/>
     </row>
     <row r="23" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="52" t="s">
-        <v>126</v>
+      <c r="A23" s="55" t="s">
+        <v>92</v>
       </c>
-      <c r="B23" s="52">
-        <v>0</v>
+      <c r="B23" s="57" t="s">
+        <v>135</v>
       </c>
-      <c r="C23"/>
-      <c r="D23" s="42"/>
+      <c r="C23" s="51"/>
       <c r="E23" s="42"/>
       <c r="F23" s="42"/>
       <c r="G23" s="42"/>
@@ -2358,19 +2328,19 @@
     </row>
     <row r="24" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="55" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="B24" s="56" t="s">
-        <v>91</v>
+        <v>135</v>
       </c>
       <c r="C24" s="51"/>
     </row>
     <row r="25" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="55" t="s">
-        <v>92</v>
+      <c r="A25" s="58" t="s">
+        <v>121</v>
       </c>
       <c r="B25" s="57" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C25" s="51"/>
       <c r="E25" s="42"/>
@@ -2397,22 +2367,45 @@
       <c r="Z25" s="42"/>
     </row>
     <row r="26" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="55" t="s">
-        <v>76</v>
+      <c r="A26" s="58" t="s">
+        <v>198</v>
       </c>
-      <c r="B26" s="56" t="s">
-        <v>140</v>
+      <c r="B26" s="58">
+        <v>0</v>
       </c>
       <c r="C26" s="51"/>
+      <c r="E26" s="42"/>
+      <c r="F26" s="42"/>
+      <c r="G26" s="42"/>
+      <c r="H26" s="42"/>
+      <c r="I26" s="42"/>
+      <c r="J26" s="42"/>
+      <c r="K26" s="42"/>
+      <c r="L26" s="42"/>
+      <c r="M26" s="42"/>
+      <c r="N26" s="42"/>
+      <c r="O26" s="42"/>
+      <c r="P26" s="42"/>
+      <c r="Q26" s="42"/>
+      <c r="R26" s="42"/>
+      <c r="S26" s="42"/>
+      <c r="T26" s="42"/>
+      <c r="U26" s="42"/>
+      <c r="V26" s="42"/>
+      <c r="W26" s="42"/>
+      <c r="X26" s="42"/>
+      <c r="Y26" s="42"/>
+      <c r="Z26" s="42"/>
     </row>
     <row r="27" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="58" t="s">
-        <v>124</v>
+      <c r="A27" s="59" t="s">
+        <v>82</v>
       </c>
-      <c r="B27" s="57" t="s">
-        <v>146</v>
+      <c r="B27" s="60" t="s">
+        <v>90</v>
       </c>
-      <c r="C27" s="51"/>
+      <c r="C27" s="61"/>
+      <c r="D27" s="42"/>
       <c r="E27" s="42"/>
       <c r="F27" s="42"/>
       <c r="G27" s="42"/>
@@ -2437,13 +2430,14 @@
       <c r="Z27" s="42"/>
     </row>
     <row r="28" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="58" t="s">
-        <v>120</v>
+      <c r="A28" s="62" t="s">
+        <v>93</v>
       </c>
-      <c r="B28" s="58">
-        <v>0</v>
+      <c r="B28" s="62" t="s">
+        <v>97</v>
       </c>
-      <c r="C28" s="51"/>
+      <c r="C28" s="49"/>
+      <c r="D28" s="42"/>
       <c r="E28" s="42"/>
       <c r="F28" s="42"/>
       <c r="G28" s="42"/>
@@ -2469,10 +2463,10 @@
     </row>
     <row r="29" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="59" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
-      <c r="B29" s="60" t="s">
-        <v>90</v>
+      <c r="B29" s="63" t="s">
+        <v>73</v>
       </c>
       <c r="C29" s="61"/>
       <c r="D29" s="42"/>
@@ -2501,10 +2495,10 @@
     </row>
     <row r="30" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="62" t="s">
-        <v>93</v>
+        <v>122</v>
       </c>
       <c r="B30" s="62" t="s">
-        <v>97</v>
+        <v>141</v>
       </c>
       <c r="C30" s="49"/>
       <c r="D30" s="42"/>
@@ -2531,14 +2525,14 @@
       <c r="Y30" s="42"/>
       <c r="Z30" s="42"/>
     </row>
-    <row r="31" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="59" t="s">
-        <v>77</v>
+    <row r="31" spans="1:26" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="65" t="s">
+        <v>197</v>
       </c>
-      <c r="B31" s="63" t="s">
-        <v>73</v>
+      <c r="B31" s="62">
+        <v>100</v>
       </c>
-      <c r="C31" s="61"/>
+      <c r="C31" s="50"/>
       <c r="D31" s="42"/>
       <c r="E31" s="42"/>
       <c r="F31" s="42"/>
@@ -2563,14 +2557,14 @@
       <c r="Y31" s="42"/>
       <c r="Z31" s="42"/>
     </row>
-    <row r="32" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="62" t="s">
-        <v>125</v>
+    <row r="32" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="68" t="s">
+        <v>127</v>
       </c>
-      <c r="B32" s="62" t="s">
-        <v>146</v>
+      <c r="B32" s="64" t="s">
+        <v>63</v>
       </c>
-      <c r="C32" s="49"/>
+      <c r="C32"/>
       <c r="D32" s="42"/>
       <c r="E32" s="42"/>
       <c r="F32" s="42"/>
@@ -2595,14 +2589,14 @@
       <c r="Y32" s="42"/>
       <c r="Z32" s="42"/>
     </row>
-    <row r="33" spans="1:26" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="65" t="s">
-        <v>121</v>
+    <row r="33" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="52" t="s">
+        <v>104</v>
       </c>
-      <c r="B33" s="62">
-        <v>100</v>
+      <c r="B33" s="52" t="s">
+        <v>71</v>
       </c>
-      <c r="C33" s="50"/>
+      <c r="C33"/>
       <c r="D33" s="42"/>
       <c r="E33" s="42"/>
       <c r="F33" s="42"/>
@@ -2628,11 +2622,11 @@
       <c r="Z33" s="42"/>
     </row>
     <row r="34" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="68" t="s">
-        <v>131</v>
+      <c r="A34" s="53" t="s">
+        <v>117</v>
       </c>
-      <c r="B34" s="64" t="s">
-        <v>63</v>
+      <c r="B34" s="54" t="s">
+        <v>189</v>
       </c>
       <c r="C34"/>
       <c r="D34" s="42"/>
@@ -2661,10 +2655,10 @@
     </row>
     <row r="35" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="52" t="s">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="B35" s="52" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C35"/>
       <c r="D35" s="42"/>
@@ -2691,12 +2685,12 @@
       <c r="Y35" s="42"/>
       <c r="Z35" s="42"/>
     </row>
-    <row r="36" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="52" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
-      <c r="B36" s="52" t="s">
-        <v>196</v>
+      <c r="B36" s="52">
+        <v>0</v>
       </c>
       <c r="C36"/>
       <c r="D36" s="42"/>
@@ -2724,13 +2718,12 @@
       <c r="Z36" s="42"/>
     </row>
     <row r="37" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="53" t="s">
-        <v>118</v>
+      <c r="A37" s="55" t="s">
+        <v>81</v>
       </c>
-      <c r="B37" s="54" t="s">
-        <v>194</v>
+      <c r="B37" s="56" t="s">
+        <v>91</v>
       </c>
-      <c r="C37"/>
       <c r="D37" s="42"/>
       <c r="E37" s="42"/>
       <c r="F37" s="42"/>
@@ -2756,13 +2749,12 @@
       <c r="Z37" s="42"/>
     </row>
     <row r="38" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="52" t="s">
-        <v>117</v>
+      <c r="A38" s="55" t="s">
+        <v>92</v>
       </c>
-      <c r="B38" s="52" t="s">
-        <v>98</v>
+      <c r="B38" s="57" t="s">
+        <v>135</v>
       </c>
-      <c r="C38"/>
       <c r="D38" s="42"/>
       <c r="E38" s="42"/>
       <c r="F38" s="42"/>
@@ -2788,13 +2780,12 @@
       <c r="Z38" s="42"/>
     </row>
     <row r="39" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="52" t="s">
-        <v>78</v>
+      <c r="A39" s="55" t="s">
+        <v>76</v>
       </c>
-      <c r="B39" s="52" t="s">
-        <v>73</v>
+      <c r="B39" s="56" t="s">
+        <v>135</v>
       </c>
-      <c r="C39"/>
       <c r="D39" s="42"/>
       <c r="E39" s="42"/>
       <c r="F39" s="42"/>
@@ -2820,13 +2811,12 @@
       <c r="Z39" s="42"/>
     </row>
     <row r="40" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="52" t="s">
-        <v>126</v>
+      <c r="A40" s="58" t="s">
+        <v>121</v>
       </c>
-      <c r="B40" s="52">
-        <v>0</v>
+      <c r="B40" s="57" t="s">
+        <v>141</v>
       </c>
-      <c r="C40"/>
       <c r="D40" s="42"/>
       <c r="E40" s="42"/>
       <c r="F40" s="42"/>
@@ -2852,12 +2842,13 @@
       <c r="Z40" s="42"/>
     </row>
     <row r="41" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="55" t="s">
-        <v>81</v>
+      <c r="A41" s="58" t="s">
+        <v>198</v>
       </c>
-      <c r="B41" s="56" t="s">
-        <v>91</v>
+      <c r="B41" s="58">
+        <v>0</v>
       </c>
+      <c r="C41" s="42"/>
       <c r="D41" s="42"/>
       <c r="E41" s="42"/>
       <c r="F41" s="42"/>
@@ -2883,12 +2874,13 @@
       <c r="Z41" s="42"/>
     </row>
     <row r="42" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="55" t="s">
-        <v>92</v>
+      <c r="A42" s="59" t="s">
+        <v>82</v>
       </c>
-      <c r="B42" s="57" t="s">
-        <v>140</v>
+      <c r="B42" s="60" t="s">
+        <v>90</v>
       </c>
+      <c r="C42" s="42"/>
       <c r="D42" s="42"/>
       <c r="E42" s="42"/>
       <c r="F42" s="42"/>
@@ -2914,12 +2906,13 @@
       <c r="Z42" s="42"/>
     </row>
     <row r="43" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="55" t="s">
-        <v>76</v>
+      <c r="A43" s="62" t="s">
+        <v>93</v>
       </c>
-      <c r="B43" s="56" t="s">
-        <v>140</v>
+      <c r="B43" s="62" t="s">
+        <v>97</v>
       </c>
+      <c r="C43" s="42"/>
       <c r="D43" s="42"/>
       <c r="E43" s="42"/>
       <c r="F43" s="42"/>
@@ -2945,12 +2938,13 @@
       <c r="Z43" s="42"/>
     </row>
     <row r="44" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="58" t="s">
-        <v>124</v>
+      <c r="A44" s="59" t="s">
+        <v>77</v>
       </c>
-      <c r="B44" s="57" t="s">
-        <v>146</v>
+      <c r="B44" s="63" t="s">
+        <v>73</v>
       </c>
+      <c r="C44" s="42"/>
       <c r="D44" s="42"/>
       <c r="E44" s="42"/>
       <c r="F44" s="42"/>
@@ -2976,11 +2970,11 @@
       <c r="Z44" s="42"/>
     </row>
     <row r="45" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="58" t="s">
-        <v>120</v>
+      <c r="A45" s="62" t="s">
+        <v>122</v>
       </c>
-      <c r="B45" s="58">
-        <v>0</v>
+      <c r="B45" s="62" t="s">
+        <v>141</v>
       </c>
       <c r="C45" s="42"/>
       <c r="D45" s="42"/>
@@ -3007,14 +3001,14 @@
       <c r="Y45" s="42"/>
       <c r="Z45" s="42"/>
     </row>
-    <row r="46" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="59" t="s">
-        <v>82</v>
+    <row r="46" spans="1:26" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="65" t="s">
+        <v>197</v>
       </c>
-      <c r="B46" s="60" t="s">
-        <v>90</v>
+      <c r="B46" s="65">
+        <v>600</v>
       </c>
-      <c r="C46" s="42"/>
+      <c r="C46" s="50"/>
       <c r="D46" s="42"/>
       <c r="E46" s="42"/>
       <c r="F46" s="42"/>
@@ -3040,13 +3034,13 @@
       <c r="Z46" s="42"/>
     </row>
     <row r="47" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="62" t="s">
-        <v>93</v>
+      <c r="A47" s="68" t="s">
+        <v>127</v>
       </c>
-      <c r="B47" s="62" t="s">
-        <v>97</v>
+      <c r="B47" s="64" t="s">
+        <v>60</v>
       </c>
-      <c r="C47" s="42"/>
+      <c r="C47"/>
       <c r="D47" s="42"/>
       <c r="E47" s="42"/>
       <c r="F47" s="42"/>
@@ -3072,13 +3066,13 @@
       <c r="Z47" s="42"/>
     </row>
     <row r="48" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="59" t="s">
-        <v>77</v>
+      <c r="A48" s="52" t="s">
+        <v>104</v>
       </c>
-      <c r="B48" s="63" t="s">
-        <v>73</v>
+      <c r="B48" s="52" t="s">
+        <v>152</v>
       </c>
-      <c r="C48" s="42"/>
+      <c r="C48"/>
       <c r="D48" s="42"/>
       <c r="E48" s="42"/>
       <c r="F48" s="42"/>
@@ -3104,13 +3098,13 @@
       <c r="Z48" s="42"/>
     </row>
     <row r="49" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="62" t="s">
-        <v>125</v>
+      <c r="A49" s="53" t="s">
+        <v>117</v>
       </c>
-      <c r="B49" s="62" t="s">
-        <v>146</v>
+      <c r="B49" s="54" t="s">
+        <v>113</v>
       </c>
-      <c r="C49" s="42"/>
+      <c r="C49"/>
       <c r="D49" s="42"/>
       <c r="E49" s="42"/>
       <c r="F49" s="42"/>
@@ -3135,14 +3129,14 @@
       <c r="Y49" s="42"/>
       <c r="Z49" s="42"/>
     </row>
-    <row r="50" spans="1:26" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="65" t="s">
-        <v>121</v>
+    <row r="50" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="52" t="s">
+        <v>78</v>
       </c>
-      <c r="B50" s="65">
-        <v>600</v>
+      <c r="B50" s="52" t="s">
+        <v>73</v>
       </c>
-      <c r="C50" s="50"/>
+      <c r="C50"/>
       <c r="D50" s="42"/>
       <c r="E50" s="42"/>
       <c r="F50" s="42"/>
@@ -3168,11 +3162,11 @@
       <c r="Z50" s="42"/>
     </row>
     <row r="51" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="68" t="s">
-        <v>131</v>
+      <c r="A51" s="52" t="s">
+        <v>199</v>
       </c>
-      <c r="B51" s="64" t="s">
-        <v>60</v>
+      <c r="B51" s="52">
+        <v>0</v>
       </c>
       <c r="C51"/>
       <c r="D51" s="42"/>
@@ -3200,13 +3194,12 @@
       <c r="Z51" s="42"/>
     </row>
     <row r="52" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="52" t="s">
-        <v>104</v>
+      <c r="A52" s="55" t="s">
+        <v>81</v>
       </c>
-      <c r="B52" s="52" t="s">
-        <v>157</v>
+      <c r="B52" s="56" t="s">
+        <v>135</v>
       </c>
-      <c r="C52"/>
       <c r="D52" s="42"/>
       <c r="E52" s="42"/>
       <c r="F52" s="42"/>
@@ -3231,14 +3224,13 @@
       <c r="Y52" s="42"/>
       <c r="Z52" s="42"/>
     </row>
-    <row r="53" spans="1:26" ht="25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="52" t="s">
-        <v>200</v>
+    <row r="53" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="55" t="s">
+        <v>92</v>
       </c>
-      <c r="B53" s="52" t="s">
-        <v>140</v>
+      <c r="B53" s="57" t="s">
+        <v>135</v>
       </c>
-      <c r="C53"/>
       <c r="D53" s="42"/>
       <c r="E53" s="42"/>
       <c r="F53" s="42"/>
@@ -3264,13 +3256,12 @@
       <c r="Z53" s="42"/>
     </row>
     <row r="54" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="53" t="s">
-        <v>118</v>
+      <c r="A54" s="55" t="s">
+        <v>76</v>
       </c>
-      <c r="B54" s="54" t="s">
-        <v>113</v>
+      <c r="B54" s="56" t="s">
+        <v>135</v>
       </c>
-      <c r="C54"/>
       <c r="D54" s="42"/>
       <c r="E54" s="42"/>
       <c r="F54" s="42"/>
@@ -3296,13 +3287,10 @@
       <c r="Z54" s="42"/>
     </row>
     <row r="55" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="52" t="s">
-        <v>117</v>
+      <c r="A55" s="58" t="s">
+        <v>121</v>
       </c>
-      <c r="B55" s="52" t="s">
-        <v>99</v>
-      </c>
-      <c r="C55"/>
+      <c r="B55" s="57"/>
       <c r="D55" s="42"/>
       <c r="E55" s="42"/>
       <c r="F55" s="42"/>
@@ -3328,13 +3316,11 @@
       <c r="Z55" s="42"/>
     </row>
     <row r="56" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="52" t="s">
-        <v>78</v>
+      <c r="A56" s="58" t="s">
+        <v>198</v>
       </c>
-      <c r="B56" s="52" t="s">
-        <v>73</v>
-      </c>
-      <c r="C56"/>
+      <c r="B56" s="58"/>
+      <c r="C56" s="42"/>
       <c r="D56" s="42"/>
       <c r="E56" s="42"/>
       <c r="F56" s="42"/>
@@ -3360,13 +3346,13 @@
       <c r="Z56" s="42"/>
     </row>
     <row r="57" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="52" t="s">
-        <v>126</v>
+      <c r="A57" s="59" t="s">
+        <v>82</v>
       </c>
-      <c r="B57" s="52">
-        <v>0</v>
+      <c r="B57" s="60" t="s">
+        <v>135</v>
       </c>
-      <c r="C57"/>
+      <c r="C57" s="42"/>
       <c r="D57" s="42"/>
       <c r="E57" s="42"/>
       <c r="F57" s="42"/>
@@ -3392,12 +3378,13 @@
       <c r="Z57" s="42"/>
     </row>
     <row r="58" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="55" t="s">
-        <v>81</v>
+      <c r="A58" s="62" t="s">
+        <v>93</v>
       </c>
-      <c r="B58" s="56" t="s">
-        <v>140</v>
+      <c r="B58" s="62" t="s">
+        <v>135</v>
       </c>
+      <c r="C58" s="42"/>
       <c r="D58" s="42"/>
       <c r="E58" s="42"/>
       <c r="F58" s="42"/>
@@ -3423,12 +3410,13 @@
       <c r="Z58" s="42"/>
     </row>
     <row r="59" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="55" t="s">
-        <v>92</v>
+      <c r="A59" s="59" t="s">
+        <v>77</v>
       </c>
-      <c r="B59" s="57" t="s">
-        <v>140</v>
+      <c r="B59" s="63" t="s">
+        <v>135</v>
       </c>
+      <c r="C59" s="42"/>
       <c r="D59" s="42"/>
       <c r="E59" s="42"/>
       <c r="F59" s="42"/>
@@ -3454,12 +3442,11 @@
       <c r="Z59" s="42"/>
     </row>
     <row r="60" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="55" t="s">
-        <v>76</v>
+      <c r="A60" s="62" t="s">
+        <v>122</v>
       </c>
-      <c r="B60" s="56" t="s">
-        <v>140</v>
-      </c>
+      <c r="B60" s="62"/>
+      <c r="C60" s="42"/>
       <c r="D60" s="42"/>
       <c r="E60" s="42"/>
       <c r="F60" s="42"/>
@@ -3484,11 +3471,12 @@
       <c r="Y60" s="42"/>
       <c r="Z60" s="42"/>
     </row>
-    <row r="61" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="58" t="s">
-        <v>124</v>
+    <row r="61" spans="1:26" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="65" t="s">
+        <v>197</v>
       </c>
-      <c r="B61" s="57"/>
+      <c r="B61" s="65"/>
+      <c r="C61" s="50"/>
       <c r="D61" s="42"/>
       <c r="E61" s="42"/>
       <c r="F61" s="42"/>
@@ -3513,137 +3501,13 @@
       <c r="Y61" s="42"/>
       <c r="Z61" s="42"/>
     </row>
-    <row r="62" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="58" t="s">
-        <v>120</v>
-      </c>
-      <c r="B62" s="58"/>
-      <c r="C62" s="42"/>
-      <c r="D62" s="42"/>
-      <c r="E62" s="42"/>
-      <c r="F62" s="42"/>
-      <c r="G62" s="42"/>
-      <c r="H62" s="42"/>
-      <c r="I62" s="42"/>
-      <c r="J62" s="42"/>
-      <c r="K62" s="42"/>
-      <c r="L62" s="42"/>
-      <c r="M62" s="42"/>
-      <c r="N62" s="42"/>
-      <c r="O62" s="42"/>
-      <c r="P62" s="42"/>
-      <c r="Q62" s="42"/>
-      <c r="R62" s="42"/>
-      <c r="S62" s="42"/>
-      <c r="T62" s="42"/>
-      <c r="U62" s="42"/>
-      <c r="V62" s="42"/>
-      <c r="W62" s="42"/>
-      <c r="X62" s="42"/>
-      <c r="Y62" s="42"/>
-      <c r="Z62" s="42"/>
-    </row>
-    <row r="63" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="59" t="s">
-        <v>82</v>
-      </c>
-      <c r="B63" s="60" t="s">
-        <v>140</v>
-      </c>
-      <c r="C63" s="42"/>
-      <c r="D63" s="42"/>
-      <c r="E63" s="42"/>
-      <c r="F63" s="42"/>
-      <c r="G63" s="42"/>
-      <c r="H63" s="42"/>
-      <c r="I63" s="42"/>
-      <c r="J63" s="42"/>
-      <c r="K63" s="42"/>
-      <c r="L63" s="42"/>
-      <c r="M63" s="42"/>
-      <c r="N63" s="42"/>
-      <c r="O63" s="42"/>
-      <c r="P63" s="42"/>
-      <c r="Q63" s="42"/>
-      <c r="R63" s="42"/>
-      <c r="S63" s="42"/>
-      <c r="T63" s="42"/>
-      <c r="U63" s="42"/>
-      <c r="V63" s="42"/>
-      <c r="W63" s="42"/>
-      <c r="X63" s="42"/>
-      <c r="Y63" s="42"/>
-      <c r="Z63" s="42"/>
-    </row>
-    <row r="64" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="62" t="s">
-        <v>93</v>
-      </c>
-      <c r="B64" s="62" t="s">
-        <v>140</v>
-      </c>
-      <c r="C64" s="42"/>
-      <c r="D64" s="42"/>
-      <c r="E64" s="42"/>
-      <c r="F64" s="42"/>
-      <c r="G64" s="42"/>
-      <c r="H64" s="42"/>
-      <c r="I64" s="42"/>
-      <c r="J64" s="42"/>
-      <c r="K64" s="42"/>
-      <c r="L64" s="42"/>
-      <c r="M64" s="42"/>
-      <c r="N64" s="42"/>
-      <c r="O64" s="42"/>
-      <c r="P64" s="42"/>
-      <c r="Q64" s="42"/>
-      <c r="R64" s="42"/>
-      <c r="S64" s="42"/>
-      <c r="T64" s="42"/>
-      <c r="U64" s="42"/>
-      <c r="V64" s="42"/>
-      <c r="W64" s="42"/>
-      <c r="X64" s="42"/>
-      <c r="Y64" s="42"/>
-      <c r="Z64" s="42"/>
-    </row>
-    <row r="65" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="59" t="s">
-        <v>77</v>
-      </c>
-      <c r="B65" s="63" t="s">
-        <v>140</v>
-      </c>
-      <c r="C65" s="42"/>
-      <c r="D65" s="42"/>
-      <c r="E65" s="42"/>
-      <c r="F65" s="42"/>
-      <c r="G65" s="42"/>
-      <c r="H65" s="42"/>
-      <c r="I65" s="42"/>
-      <c r="J65" s="42"/>
-      <c r="K65" s="42"/>
-      <c r="L65" s="42"/>
-      <c r="M65" s="42"/>
-      <c r="N65" s="42"/>
-      <c r="O65" s="42"/>
-      <c r="P65" s="42"/>
-      <c r="Q65" s="42"/>
-      <c r="R65" s="42"/>
-      <c r="S65" s="42"/>
-      <c r="T65" s="42"/>
-      <c r="U65" s="42"/>
-      <c r="V65" s="42"/>
-      <c r="W65" s="42"/>
-      <c r="X65" s="42"/>
-      <c r="Y65" s="42"/>
-      <c r="Z65" s="42"/>
-    </row>
+    <row r="62" spans="1:26" s="66" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="63" spans="1:26" s="66" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" spans="1:26" s="66" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="65" spans="1:26" s="66" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="66" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="62" t="s">
-        <v>125</v>
-      </c>
-      <c r="B66" s="62"/>
+      <c r="A66" s="42"/>
+      <c r="B66" s="42"/>
       <c r="C66" s="42"/>
       <c r="D66" s="42"/>
       <c r="E66" s="42"/>
@@ -3669,12 +3533,10 @@
       <c r="Y66" s="42"/>
       <c r="Z66" s="42"/>
     </row>
-    <row r="67" spans="1:26" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="65" t="s">
-        <v>121</v>
-      </c>
-      <c r="B67" s="65"/>
-      <c r="C67" s="50"/>
+    <row r="67" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="42"/>
+      <c r="B67" s="42"/>
+      <c r="C67" s="42"/>
       <c r="D67" s="42"/>
       <c r="E67" s="42"/>
       <c r="F67" s="42"/>
@@ -3699,10 +3561,118 @@
       <c r="Y67" s="42"/>
       <c r="Z67" s="42"/>
     </row>
-    <row r="68" spans="1:26" s="66" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="69" spans="1:26" s="66" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="70" spans="1:26" s="66" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="71" spans="1:26" s="66" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="68" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="42"/>
+      <c r="B68" s="42"/>
+      <c r="C68" s="42"/>
+      <c r="D68" s="42"/>
+      <c r="E68" s="42"/>
+      <c r="F68" s="42"/>
+      <c r="G68" s="42"/>
+      <c r="H68" s="42"/>
+      <c r="I68" s="42"/>
+      <c r="J68" s="42"/>
+      <c r="K68" s="42"/>
+      <c r="L68" s="42"/>
+      <c r="M68" s="42"/>
+      <c r="N68" s="42"/>
+      <c r="O68" s="42"/>
+      <c r="P68" s="42"/>
+      <c r="Q68" s="42"/>
+      <c r="R68" s="42"/>
+      <c r="S68" s="42"/>
+      <c r="T68" s="42"/>
+      <c r="U68" s="42"/>
+      <c r="V68" s="42"/>
+      <c r="W68" s="42"/>
+      <c r="X68" s="42"/>
+      <c r="Y68" s="42"/>
+      <c r="Z68" s="42"/>
+    </row>
+    <row r="69" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="42"/>
+      <c r="B69" s="42"/>
+      <c r="C69" s="42"/>
+      <c r="D69" s="42"/>
+      <c r="E69" s="42"/>
+      <c r="F69" s="42"/>
+      <c r="G69" s="42"/>
+      <c r="H69" s="42"/>
+      <c r="I69" s="42"/>
+      <c r="J69" s="42"/>
+      <c r="K69" s="42"/>
+      <c r="L69" s="42"/>
+      <c r="M69" s="42"/>
+      <c r="N69" s="42"/>
+      <c r="O69" s="42"/>
+      <c r="P69" s="42"/>
+      <c r="Q69" s="42"/>
+      <c r="R69" s="42"/>
+      <c r="S69" s="42"/>
+      <c r="T69" s="42"/>
+      <c r="U69" s="42"/>
+      <c r="V69" s="42"/>
+      <c r="W69" s="42"/>
+      <c r="X69" s="42"/>
+      <c r="Y69" s="42"/>
+      <c r="Z69" s="42"/>
+    </row>
+    <row r="70" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="42"/>
+      <c r="B70" s="42"/>
+      <c r="C70" s="42"/>
+      <c r="D70" s="42"/>
+      <c r="E70" s="42"/>
+      <c r="F70" s="42"/>
+      <c r="G70" s="42"/>
+      <c r="H70" s="42"/>
+      <c r="I70" s="42"/>
+      <c r="J70" s="42"/>
+      <c r="K70" s="42"/>
+      <c r="L70" s="42"/>
+      <c r="M70" s="42"/>
+      <c r="N70" s="42"/>
+      <c r="O70" s="42"/>
+      <c r="P70" s="42"/>
+      <c r="Q70" s="42"/>
+      <c r="R70" s="42"/>
+      <c r="S70" s="42"/>
+      <c r="T70" s="42"/>
+      <c r="U70" s="42"/>
+      <c r="V70" s="42"/>
+      <c r="W70" s="42"/>
+      <c r="X70" s="42"/>
+      <c r="Y70" s="42"/>
+      <c r="Z70" s="42"/>
+    </row>
+    <row r="71" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="42"/>
+      <c r="B71" s="42"/>
+      <c r="C71" s="42"/>
+      <c r="D71" s="42"/>
+      <c r="E71" s="42"/>
+      <c r="F71" s="42"/>
+      <c r="G71" s="42"/>
+      <c r="H71" s="42"/>
+      <c r="I71" s="42"/>
+      <c r="J71" s="42"/>
+      <c r="K71" s="42"/>
+      <c r="L71" s="42"/>
+      <c r="M71" s="42"/>
+      <c r="N71" s="42"/>
+      <c r="O71" s="42"/>
+      <c r="P71" s="42"/>
+      <c r="Q71" s="42"/>
+      <c r="R71" s="42"/>
+      <c r="S71" s="42"/>
+      <c r="T71" s="42"/>
+      <c r="U71" s="42"/>
+      <c r="V71" s="42"/>
+      <c r="W71" s="42"/>
+      <c r="X71" s="42"/>
+      <c r="Y71" s="42"/>
+      <c r="Z71" s="42"/>
+    </row>
     <row r="72" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="42"/>
       <c r="B72" s="42"/>
@@ -27503,185 +27473,17 @@
       <c r="Y921" s="42"/>
       <c r="Z921" s="42"/>
     </row>
-    <row r="922" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A922" s="42"/>
-      <c r="B922" s="42"/>
-      <c r="C922" s="42"/>
-      <c r="D922" s="42"/>
-      <c r="E922" s="42"/>
-      <c r="F922" s="42"/>
-      <c r="G922" s="42"/>
-      <c r="H922" s="42"/>
-      <c r="I922" s="42"/>
-      <c r="J922" s="42"/>
-      <c r="K922" s="42"/>
-      <c r="L922" s="42"/>
-      <c r="M922" s="42"/>
-      <c r="N922" s="42"/>
-      <c r="O922" s="42"/>
-      <c r="P922" s="42"/>
-      <c r="Q922" s="42"/>
-      <c r="R922" s="42"/>
-      <c r="S922" s="42"/>
-      <c r="T922" s="42"/>
-      <c r="U922" s="42"/>
-      <c r="V922" s="42"/>
-      <c r="W922" s="42"/>
-      <c r="X922" s="42"/>
-      <c r="Y922" s="42"/>
-      <c r="Z922" s="42"/>
-    </row>
-    <row r="923" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A923" s="42"/>
-      <c r="B923" s="42"/>
-      <c r="C923" s="42"/>
-      <c r="D923" s="42"/>
-      <c r="E923" s="42"/>
-      <c r="F923" s="42"/>
-      <c r="G923" s="42"/>
-      <c r="H923" s="42"/>
-      <c r="I923" s="42"/>
-      <c r="J923" s="42"/>
-      <c r="K923" s="42"/>
-      <c r="L923" s="42"/>
-      <c r="M923" s="42"/>
-      <c r="N923" s="42"/>
-      <c r="O923" s="42"/>
-      <c r="P923" s="42"/>
-      <c r="Q923" s="42"/>
-      <c r="R923" s="42"/>
-      <c r="S923" s="42"/>
-      <c r="T923" s="42"/>
-      <c r="U923" s="42"/>
-      <c r="V923" s="42"/>
-      <c r="W923" s="42"/>
-      <c r="X923" s="42"/>
-      <c r="Y923" s="42"/>
-      <c r="Z923" s="42"/>
-    </row>
-    <row r="924" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A924" s="42"/>
-      <c r="B924" s="42"/>
-      <c r="C924" s="42"/>
-      <c r="D924" s="42"/>
-      <c r="E924" s="42"/>
-      <c r="F924" s="42"/>
-      <c r="G924" s="42"/>
-      <c r="H924" s="42"/>
-      <c r="I924" s="42"/>
-      <c r="J924" s="42"/>
-      <c r="K924" s="42"/>
-      <c r="L924" s="42"/>
-      <c r="M924" s="42"/>
-      <c r="N924" s="42"/>
-      <c r="O924" s="42"/>
-      <c r="P924" s="42"/>
-      <c r="Q924" s="42"/>
-      <c r="R924" s="42"/>
-      <c r="S924" s="42"/>
-      <c r="T924" s="42"/>
-      <c r="U924" s="42"/>
-      <c r="V924" s="42"/>
-      <c r="W924" s="42"/>
-      <c r="X924" s="42"/>
-      <c r="Y924" s="42"/>
-      <c r="Z924" s="42"/>
-    </row>
-    <row r="925" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A925" s="42"/>
-      <c r="B925" s="42"/>
-      <c r="C925" s="42"/>
-      <c r="D925" s="42"/>
-      <c r="E925" s="42"/>
-      <c r="F925" s="42"/>
-      <c r="G925" s="42"/>
-      <c r="H925" s="42"/>
-      <c r="I925" s="42"/>
-      <c r="J925" s="42"/>
-      <c r="K925" s="42"/>
-      <c r="L925" s="42"/>
-      <c r="M925" s="42"/>
-      <c r="N925" s="42"/>
-      <c r="O925" s="42"/>
-      <c r="P925" s="42"/>
-      <c r="Q925" s="42"/>
-      <c r="R925" s="42"/>
-      <c r="S925" s="42"/>
-      <c r="T925" s="42"/>
-      <c r="U925" s="42"/>
-      <c r="V925" s="42"/>
-      <c r="W925" s="42"/>
-      <c r="X925" s="42"/>
-      <c r="Y925" s="42"/>
-      <c r="Z925" s="42"/>
-    </row>
-    <row r="926" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A926" s="42"/>
-      <c r="B926" s="42"/>
-      <c r="C926" s="42"/>
-      <c r="D926" s="42"/>
-      <c r="E926" s="42"/>
-      <c r="F926" s="42"/>
-      <c r="G926" s="42"/>
-      <c r="H926" s="42"/>
-      <c r="I926" s="42"/>
-      <c r="J926" s="42"/>
-      <c r="K926" s="42"/>
-      <c r="L926" s="42"/>
-      <c r="M926" s="42"/>
-      <c r="N926" s="42"/>
-      <c r="O926" s="42"/>
-      <c r="P926" s="42"/>
-      <c r="Q926" s="42"/>
-      <c r="R926" s="42"/>
-      <c r="S926" s="42"/>
-      <c r="T926" s="42"/>
-      <c r="U926" s="42"/>
-      <c r="V926" s="42"/>
-      <c r="W926" s="42"/>
-      <c r="X926" s="42"/>
-      <c r="Y926" s="42"/>
-      <c r="Z926" s="42"/>
-    </row>
-    <row r="927" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A927" s="42"/>
-      <c r="B927" s="42"/>
-      <c r="C927" s="42"/>
-      <c r="D927" s="42"/>
-      <c r="E927" s="42"/>
-      <c r="F927" s="42"/>
-      <c r="G927" s="42"/>
-      <c r="H927" s="42"/>
-      <c r="I927" s="42"/>
-      <c r="J927" s="42"/>
-      <c r="K927" s="42"/>
-      <c r="L927" s="42"/>
-      <c r="M927" s="42"/>
-      <c r="N927" s="42"/>
-      <c r="O927" s="42"/>
-      <c r="P927" s="42"/>
-      <c r="Q927" s="42"/>
-      <c r="R927" s="42"/>
-      <c r="S927" s="42"/>
-      <c r="T927" s="42"/>
-      <c r="U927" s="42"/>
-      <c r="V927" s="42"/>
-      <c r="W927" s="42"/>
-      <c r="X927" s="42"/>
-      <c r="Y927" s="42"/>
-      <c r="Z927" s="42"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="21">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="17">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9269EC84-DF31-1A4B-A990-FD99E0DF6A37}">
           <x14:formula1>
             <xm:f>Lists!$F$2:$F$10</xm:f>
           </x14:formula1>
-          <xm:sqref>B30 B25 B47 B42 B64 B59</xm:sqref>
+          <xm:sqref>B28 B23 B43 B38 B58 B53</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F48AC468-AC67-414F-A31D-152D1C1A14B8}">
           <x14:formula1>
@@ -27693,7 +27495,7 @@
           <x14:formula1>
             <xm:f>Lists!$G$2:$G$5</xm:f>
           </x14:formula1>
-          <xm:sqref>B41 B46 B58 B63 B24 B29</xm:sqref>
+          <xm:sqref>B37 B42 B52 B57 B22 B27</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{FFB11884-705E-4C4B-9963-11B4FBF86EFD}">
           <x14:formula1>
@@ -27717,7 +27519,7 @@
           <x14:formula1>
             <xm:f>Lists!$E$2:$E$6</xm:f>
           </x14:formula1>
-          <xm:sqref>B26 B31 B43 B48 B22 B60 B65 B39 B56</xm:sqref>
+          <xm:sqref>B24 B29 B39 B44 B20 B54 B59 B35 B50</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{8B68413C-BA2E-3E4F-BCCD-63E54D16131E}">
           <x14:formula1>
@@ -27729,31 +27531,19 @@
           <x14:formula1>
             <xm:f>Lists!$G$3:$G$5</xm:f>
           </x14:formula1>
-          <xm:sqref>B41 B58</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{C159AD43-387F-8A44-88E8-16412071B24C}">
-          <x14:formula1>
-            <xm:f>Lists!$C$2:$C$6</xm:f>
-          </x14:formula1>
-          <xm:sqref>B55 B21 B38</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FF158337-349C-AE45-9DC7-81D1DD942C51}">
-          <x14:formula1>
-            <xm:f>Lists!$C$2:$C$9</xm:f>
-          </x14:formula1>
-          <xm:sqref>B38 B55 B21</xm:sqref>
+          <xm:sqref>B37 B52</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8F92160A-7435-3B42-84F3-7B849CE421F0}">
           <x14:formula1>
             <xm:f>Lists!$H$2:$H$7</xm:f>
           </x14:formula1>
-          <xm:sqref>B34 B17 B51</xm:sqref>
+          <xm:sqref>B32 B17 B47</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{209ABDC6-7A4F-1043-BD31-F5067EDD9592}">
           <x14:formula1>
             <xm:f>Lists!$D$2:$D$27</xm:f>
           </x14:formula1>
-          <xm:sqref>B37 B20 B54</xm:sqref>
+          <xm:sqref>B34 B19 B49</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{4DE4111E-DA5E-784E-9D6F-05103F7D2493}">
           <x14:formula1>
@@ -27761,41 +27551,29 @@
           </x14:formula1>
           <xm:sqref>B14</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{458F1957-7F4C-3843-8AFA-688CEDE96E83}">
-          <x14:formula1>
-            <xm:f>Lists!$N$2:$N$7</xm:f>
-          </x14:formula1>
-          <xm:sqref>B19 B53 B36</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B241593E-F5D9-0643-9841-833D07C14BE8}">
-          <x14:formula1>
-            <xm:f>Lists!$N$2:$N$7</xm:f>
-          </x14:formula1>
-          <xm:sqref>B19 B53 B36</xm:sqref>
-        </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{970994F8-0C5A-954C-8A5B-082DB9E55E96}">
           <x14:formula1>
             <xm:f>Lists!$B$2:$B$27</xm:f>
           </x14:formula1>
-          <xm:sqref>B35 B52 B18</xm:sqref>
+          <xm:sqref>B33 B48 B18</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E36366AC-D6BD-7D4B-94C1-F87AEC17F439}">
           <x14:formula1>
             <xm:f>Lists!$B$3:$B$17</xm:f>
           </x14:formula1>
-          <xm:sqref>B52</xm:sqref>
+          <xm:sqref>B48</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F9DEF641-EE3D-B047-8D16-CAC81DB4BCBD}">
           <x14:formula1>
             <xm:f>Lists!$B$2:$B$17</xm:f>
           </x14:formula1>
-          <xm:sqref>B35 B52</xm:sqref>
+          <xm:sqref>B33 B48</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C377399E-4DEA-7E44-B16E-7301589BBC04}">
           <x14:formula1>
             <xm:f>Lists!$B$3:$B$27</xm:f>
           </x14:formula1>
-          <xm:sqref>B35</xm:sqref>
+          <xm:sqref>B33</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4B8BFAEF-3C0C-4641-836E-A751B7E93527}">
           <x14:formula1>
@@ -42065,10 +41843,10 @@
         <v>105</v>
       </c>
       <c r="D1" s="73" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="E1" s="74" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="F1" s="73" t="s">
         <v>94</v>
@@ -42092,33 +41870,33 @@
         <v>55</v>
       </c>
       <c r="M1" s="74" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="N1" s="74" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="66" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B2" s="66" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C2" s="66" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D2" s="66" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="E2" s="66" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F2" s="66" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="G2" s="66" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="H2" s="66" t="s">
         <v>58</v>
@@ -42136,24 +41914,24 @@
         <v>70</v>
       </c>
       <c r="M2" s="75" t="s">
+        <v>131</v>
+      </c>
+      <c r="N2" s="66" t="s">
         <v>135</v>
       </c>
-      <c r="N2" s="66" t="s">
-        <v>140</v>
-      </c>
     </row>
     <row r="3" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="66" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B3" s="66" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C3" s="66" t="s">
         <v>98</v>
       </c>
       <c r="D3" s="66" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="E3" s="66" t="s">
         <v>74</v>
@@ -42177,13 +41955,13 @@
         <v>61</v>
       </c>
       <c r="L3" s="66" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="M3" s="75" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="N3" s="66" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -42194,10 +41972,10 @@
         <v>101</v>
       </c>
       <c r="C4" s="66" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="D4" s="66" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="E4" s="66" t="s">
         <v>73</v>
@@ -42221,11 +41999,11 @@
         <v>103</v>
       </c>
       <c r="L4" s="66" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="M4" s="66"/>
       <c r="N4" s="66" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -42237,7 +42015,7 @@
         <v>99</v>
       </c>
       <c r="D5" s="66" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="E5" s="66" t="s">
         <v>79</v>
@@ -42257,23 +42035,23 @@
         <v>69</v>
       </c>
       <c r="L5" s="66" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="M5" s="66"/>
       <c r="N5" s="66" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="66"/>
       <c r="B6" s="66" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C6" s="66" t="s">
         <v>69</v>
       </c>
       <c r="D6" s="66" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="E6" s="66" t="s">
         <v>69</v>
@@ -42283,23 +42061,23 @@
       </c>
       <c r="G6" s="66"/>
       <c r="H6" s="66" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="I6" s="66"/>
       <c r="J6" s="66"/>
       <c r="K6" s="66"/>
       <c r="L6" s="66" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="M6" s="66"/>
       <c r="N6" s="66" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="66"/>
       <c r="B7" s="76" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C7" s="66"/>
       <c r="D7" s="66" t="s">
@@ -42311,13 +42089,13 @@
       </c>
       <c r="G7" s="66"/>
       <c r="H7" s="66" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="I7" s="66"/>
       <c r="J7" s="66"/>
       <c r="K7" s="66"/>
       <c r="L7" s="66" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="M7" s="66"/>
       <c r="N7" s="66" t="s">
@@ -42327,7 +42105,7 @@
     <row r="8" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="66"/>
       <c r="B8" s="66" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C8" s="66"/>
       <c r="D8" s="66" t="s">
@@ -42345,14 +42123,14 @@
       <c r="J8" s="66"/>
       <c r="K8" s="66"/>
       <c r="L8" s="66" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="M8" s="66"/>
     </row>
     <row r="9" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="66"/>
       <c r="B9" s="66" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C9" s="66"/>
       <c r="D9" s="66" t="s">
@@ -42370,18 +42148,18 @@
       <c r="J9" s="66"/>
       <c r="K9" s="66"/>
       <c r="L9" s="66" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="M9" s="66"/>
     </row>
     <row r="10" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="66"/>
       <c r="B10" s="76" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="C10" s="66"/>
       <c r="D10" s="66" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="E10" s="66"/>
       <c r="F10" s="66" t="s">
@@ -42393,18 +42171,18 @@
       <c r="J10" s="66"/>
       <c r="K10" s="66"/>
       <c r="L10" s="66" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="M10" s="66"/>
     </row>
     <row r="11" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="66"/>
       <c r="B11" s="76" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C11" s="66"/>
       <c r="D11" s="66" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="E11" s="66"/>
       <c r="F11" s="66"/>
@@ -42414,18 +42192,18 @@
       <c r="J11" s="66"/>
       <c r="K11" s="66"/>
       <c r="L11" s="66" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="M11" s="66"/>
     </row>
     <row r="12" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="66"/>
       <c r="B12" s="66" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="C12" s="66"/>
       <c r="D12" s="66" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="E12" s="66"/>
       <c r="F12" s="66"/>
@@ -42435,18 +42213,18 @@
       <c r="J12" s="66"/>
       <c r="K12" s="66"/>
       <c r="L12" s="66" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="M12" s="66"/>
     </row>
     <row r="13" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="66"/>
       <c r="B13" s="66" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C13" s="66"/>
       <c r="D13" s="66" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="E13" s="66"/>
       <c r="F13" s="66"/>
@@ -42456,18 +42234,18 @@
       <c r="J13" s="66"/>
       <c r="K13" s="66"/>
       <c r="L13" s="66" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="M13" s="66"/>
     </row>
     <row r="14" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="66"/>
       <c r="B14" s="66" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C14" s="66"/>
       <c r="D14" s="66" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="E14" s="66"/>
       <c r="F14" s="66"/>
@@ -42477,18 +42255,18 @@
       <c r="J14" s="66"/>
       <c r="K14" s="66"/>
       <c r="L14" s="66" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="M14" s="66"/>
     </row>
     <row r="15" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="66"/>
       <c r="B15" s="66" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="C15" s="66"/>
       <c r="D15" s="66" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="E15" s="66"/>
       <c r="F15" s="66"/>
@@ -42498,18 +42276,18 @@
       <c r="J15" s="66"/>
       <c r="K15" s="66"/>
       <c r="L15" s="66" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="M15" s="66"/>
     </row>
     <row r="16" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="66"/>
       <c r="B16" s="66" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="C16" s="66"/>
       <c r="D16" s="66" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="E16" s="66"/>
       <c r="F16" s="66"/>
@@ -42519,18 +42297,18 @@
       <c r="J16" s="66"/>
       <c r="K16" s="66"/>
       <c r="L16" s="66" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="M16" s="66"/>
     </row>
     <row r="17" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="66"/>
       <c r="B17" s="66" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C17" s="66"/>
       <c r="D17" s="66" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="E17" s="66"/>
       <c r="F17" s="66"/>
@@ -42561,14 +42339,14 @@
       <c r="J18" s="66"/>
       <c r="K18" s="66"/>
       <c r="L18" s="66" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="M18" s="66"/>
     </row>
     <row r="19" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="66"/>
       <c r="B19" s="66" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C19" s="66"/>
       <c r="D19" s="66" t="s">
@@ -42586,7 +42364,7 @@
     <row r="20" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="66"/>
       <c r="B20" s="66" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C20" s="66"/>
       <c r="D20" s="66" t="s">
@@ -42604,7 +42382,7 @@
     <row r="21" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="66"/>
       <c r="B21" s="76" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C21" s="66"/>
       <c r="D21" s="66" t="s">
@@ -42623,7 +42401,7 @@
     <row r="22" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="66"/>
       <c r="B22" s="76" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C22" s="66"/>
       <c r="D22" s="66" t="s">
@@ -42642,7 +42420,7 @@
     <row r="23" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="66"/>
       <c r="B23" s="76" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C23" s="66"/>
       <c r="D23" s="66" t="s">
@@ -42661,7 +42439,7 @@
     <row r="24" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="66"/>
       <c r="B24" s="76" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="C24" s="66"/>
       <c r="D24" s="66" t="s">
@@ -42680,7 +42458,7 @@
     <row r="25" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="66"/>
       <c r="B25" s="76" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="C25" s="66"/>
       <c r="D25" s="66" t="s">
@@ -42701,7 +42479,7 @@
         <v>71</v>
       </c>
       <c r="D26" s="66" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
